--- a/artfynd/A 63685-2023 artfynd.xlsx
+++ b/artfynd/A 63685-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>123625661</v>
       </c>
       <c r="B3" t="n">
-        <v>58186</v>
+        <v>58192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>123625649</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
+        <v>57638</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>123625653</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 63685-2023 artfynd.xlsx
+++ b/artfynd/A 63685-2023 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123625661</v>
+        <v>123625649</v>
       </c>
       <c r="B3" t="n">
-        <v>58192</v>
+        <v>57641</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123625649</v>
+        <v>123625661</v>
       </c>
       <c r="B4" t="n">
-        <v>57638</v>
+        <v>58195</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1032,7 @@
         <v>123625653</v>
       </c>
       <c r="B5" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 63685-2023 artfynd.xlsx
+++ b/artfynd/A 63685-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>123625649</v>
       </c>
       <c r="B3" t="n">
-        <v>57641</v>
+        <v>57642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123625661</v>
+        <v>123625653</v>
       </c>
       <c r="B4" t="n">
-        <v>58195</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123625653</v>
+        <v>123625661</v>
       </c>
       <c r="B5" t="n">
-        <v>57860</v>
+        <v>58196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1041,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 63685-2023 artfynd.xlsx
+++ b/artfynd/A 63685-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,246 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123973456</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57382</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stora eken, Skinnersdal, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>452334</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6400639</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Barnarp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thomas Rosell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Rosell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123973466</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58033</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stora eken, Skinnersdal, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>452334</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6400639</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Barnarp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Rosell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Rosell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63685-2023 artfynd.xlsx
+++ b/artfynd/A 63685-2023 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123625649</v>
+        <v>123625653</v>
       </c>
       <c r="B3" t="n">
-        <v>57642</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123625653</v>
+        <v>123625649</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>57642</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,20 +921,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 63685-2023 artfynd.xlsx
+++ b/artfynd/A 63685-2023 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123625653</v>
+        <v>123625661</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>58196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123625661</v>
+        <v>123625653</v>
       </c>
       <c r="B5" t="n">
-        <v>58196</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1041,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 63685-2023 artfynd.xlsx
+++ b/artfynd/A 63685-2023 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123625661</v>
+        <v>123625653</v>
       </c>
       <c r="B3" t="n">
-        <v>58196</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123625653</v>
+        <v>123625661</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>58196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1041,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 63685-2023 artfynd.xlsx
+++ b/artfynd/A 63685-2023 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123625653</v>
+        <v>123625661</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>58196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123625661</v>
+        <v>123625653</v>
       </c>
       <c r="B5" t="n">
-        <v>58196</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1041,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123973456</v>
+        <v>123973466</v>
       </c>
       <c r="B6" t="n">
-        <v>57382</v>
+        <v>58033</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,20 +1161,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123973466</v>
+        <v>123973456</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>57382</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 63685-2023 artfynd.xlsx
+++ b/artfynd/A 63685-2023 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123973466</v>
+        <v>123973456</v>
       </c>
       <c r="B6" t="n">
-        <v>58055</v>
+        <v>57404</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,20 +1161,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123973456</v>
+        <v>123973466</v>
       </c>
       <c r="B7" t="n">
-        <v>57404</v>
+        <v>58055</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 63685-2023 artfynd.xlsx
+++ b/artfynd/A 63685-2023 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123973456</v>
+        <v>123973466</v>
       </c>
       <c r="B6" t="n">
-        <v>57404</v>
+        <v>58055</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,20 +1161,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123973466</v>
+        <v>123973456</v>
       </c>
       <c r="B7" t="n">
-        <v>58055</v>
+        <v>57404</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 63685-2023 artfynd.xlsx
+++ b/artfynd/A 63685-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116477581</v>
+        <v>123973456</v>
       </c>
       <c r="B2" t="n">
-        <v>57517</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,11 +710,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -757,12 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,32 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123625661</v>
+        <v>133297022</v>
       </c>
       <c r="B3" t="n">
-        <v>58218</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -867,22 +863,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:07</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123625653</v>
+        <v>133297023</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +916,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -987,22 +978,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123625649</v>
+        <v>133297030</v>
       </c>
       <c r="B5" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>102980</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1107,22 +1093,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,15 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123973456</v>
+        <v>123973466</v>
       </c>
       <c r="B6" t="n">
-        <v>57404</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,16 +1146,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1232,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,37 +1250,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123973466</v>
+        <v>116477581</v>
       </c>
       <c r="B7" t="n">
-        <v>58055</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1309,7 +1285,11 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1347,22 +1327,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133297023</v>
+        <v>123625653</v>
       </c>
       <c r="B8" t="n">
-        <v>57280</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,16 +1370,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100065</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1462,22 +1432,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,32 +1474,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133297022</v>
+        <v>123625649</v>
       </c>
       <c r="B9" t="n">
-        <v>57269</v>
+        <v>58112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100038</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1577,22 +1547,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1741,7 +1711,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1847,6 +1817,236 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123625661</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stora eken, Skinnersdal, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>452334</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6400639</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Barnarp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Thomas Rosell</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Thomas Rosell</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123625648</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stora eken, Skinnersdal, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>452334</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6400639</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Barnarp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Thomas Rosell</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Thomas Rosell</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63685-2023 artfynd.xlsx
+++ b/artfynd/A 63685-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123973456</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133297022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133297023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133297030</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123973466</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116477581</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123625653</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1586,6 +1626,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123625649</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1701,6 +1746,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133297036</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1816,6 +1866,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133297040</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1931,6 +1986,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123625661</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2046,8 +2106,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123625648</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>